--- a/forms_mapping.xlsx
+++ b/forms_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\Tipificador Mejor\Primigenio - soporte Hogar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\Hogar-main(2)\Hogar-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D151C0E8-D949-4AB7-8D65-65A9E9AAFE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F119AB32-2230-4904-8649-B3679B990195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="136">
   <si>
     <t>form_key</t>
   </si>
@@ -331,6 +331,120 @@
   </si>
   <si>
     <t>entry.2068363297</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>Sondeo</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLScOnqtEkPZTISXN4o3vrsi_vjMF3GcPuBlb0dIqJOuZVmeklQ/viewform</t>
+  </si>
+  <si>
+    <t>entry.5694922</t>
+  </si>
+  <si>
+    <t>entry.955460218</t>
+  </si>
+  <si>
+    <t>entry.213109764</t>
+  </si>
+  <si>
+    <t>entry.216870845</t>
+  </si>
+  <si>
+    <t>entry.575117188</t>
+  </si>
+  <si>
+    <t>entry.977079435</t>
+  </si>
+  <si>
+    <t>entry.789181094</t>
+  </si>
+  <si>
+    <t>entry.415672825</t>
+  </si>
+  <si>
+    <t>entry.44152504</t>
+  </si>
+  <si>
+    <t>entry.137275158</t>
+  </si>
+  <si>
+    <t>entry.1907905929</t>
+  </si>
+  <si>
+    <t>inconvenientes</t>
+  </si>
+  <si>
+    <t>entry.932424681</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>entry.2011962965</t>
+  </si>
+  <si>
+    <t>electrico</t>
+  </si>
+  <si>
+    <t>generador</t>
+  </si>
+  <si>
+    <t>entry.704266693</t>
+  </si>
+  <si>
+    <t>entry.1566836783</t>
+  </si>
+  <si>
+    <t>datetime;id;rut;nombre;telefonos;ont;olt;tarjeta_puerto;direccion_nodo;motivo;observaciones;notas</t>
+  </si>
+  <si>
+    <t>entry.1163287562</t>
+  </si>
+  <si>
+    <t>tarjeta_puerto</t>
+  </si>
+  <si>
+    <t>NODO: ||CTO:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ||/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/|| </t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>entry.2142598155_day</t>
+  </si>
+  <si>
+    <t>entry.2142598155_month</t>
+  </si>
+  <si>
+    <t>entry.2142598155_year</t>
+  </si>
+  <si>
+    <t>entry.2142598155_hour</t>
+  </si>
+  <si>
+    <t>entry.2142598155_minute</t>
+  </si>
+  <si>
+    <t>/||/</t>
+  </si>
+  <si>
+    <t>,||:</t>
+  </si>
+  <si>
+    <t>:||:</t>
+  </si>
+  <si>
+    <t>/6/||,</t>
   </si>
 </sst>
 </file>
@@ -668,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -734,9 +848,21 @@
         <v>94</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{ECFF7F10-9749-42B2-B6E6-73798A09F429}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{FEA23F44-238C-4CF0-97FD-E3466AB759FB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -744,7 +870,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF6FF24-64F9-4D1C-AEDC-54B01573F003}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1298,52 +1424,307 @@
         <v>93</v>
       </c>
     </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>92</v>
+      </c>
+      <c r="C60" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>112</v>
+      </c>
+      <c r="C61" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" t="s">
+        <v>129</v>
+      </c>
+      <c r="E65" t="s">
+        <v>135</v>
+      </c>
+    </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>126</v>
+      </c>
+      <c r="C66" t="s">
+        <v>98</v>
+      </c>
+      <c r="D66" t="s">
+        <v>130</v>
+      </c>
+      <c r="E66" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>126</v>
+      </c>
+      <c r="C67" t="s">
+        <v>98</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>116</v>
+      </c>
+      <c r="C68" t="s">
+        <v>98</v>
+      </c>
+      <c r="D68" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69" t="s">
-        <v>31</v>
+        <v>117</v>
+      </c>
+      <c r="C69" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>87</v>
+      </c>
+      <c r="C70" t="s">
+        <v>98</v>
+      </c>
+      <c r="D70" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>30</v>
       </c>
     </row>
